--- a/InputData/indst/_cement/CPRS/Cement Preexisting Capacity Overhaul Decision Schedule.xlsx
+++ b/InputData/indst/_cement/CPRS/Cement Preexisting Capacity Overhaul Decision Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CPRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20913215-C7E4-46C5-B85A-5EE9706C2316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3994564B-B2A5-402E-8B06-62EC789A45BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>CPRS Cement Preexisting Capacity Overhaul Decision Schedule</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Annual rate = 7% x cohort</t>
   </si>
   <si>
-    <t>Annual rate, rounded to nearest 10,000 t/yr (shipped)</t>
-  </si>
-  <si>
     <t>Years at full rate (2026-2039)</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>Remainder in 2040 (Mt) = cohort - cumulative</t>
   </si>
   <si>
-    <t>Remainder in 2040, shipped (t/yr)</t>
-  </si>
-  <si>
     <t>Post-2000 cohort: 35-yr staggered campaign end, 2036-2045</t>
   </si>
   <si>
@@ -112,9 +106,6 @@
     <t>Annual rate = cohort / years (Mt/yr)</t>
   </si>
   <si>
-    <t>Annual rate, shipped (t/yr)</t>
-  </si>
-  <si>
     <t>Year-by-year schedule (t/yr), pre-2000 + post-2000</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
   </si>
   <si>
     <t>Smoothed (t/yr)</t>
-  </si>
-  <si>
-    <t>Rounded 1,000 t</t>
   </si>
   <si>
     <t>Shipped (t/yr)</t>
@@ -254,15 +242,9 @@
     <t>U.S. values</t>
   </si>
   <si>
-    <t>The older cohort (49.6 million metric tons) comes up for decision at 7% of its capacity per year starting in 2026, which is 3.47 million metric tons per year through 2039 after rounding, with the remaining 1.02 million metric tons in 2040. The newer cohort (46.7 million metric tons) was installed over roughly 2000-2010 and reaches a 35-year campaign end across 2036-2045; we spread it evenly over those ten years, rounded to 4.7 million metric tons per year, which makes the newer cohort total 47.0 million metric tons, about 0.3 million more than the annex figure. The two cohorts overlap in 2036-2040. Turnover before 2025 is already reflected in the start-year capacity the model begins with, so nothing is scheduled before 2026.</t>
-  </si>
-  <si>
     <t>Smoothing</t>
   </si>
   <si>
-    <t>Real kilns do not all reach a decision on the same date: campaign timing varies, and ECRA documents rolling 20-30 year component replacement cycles. Using the cohort schedule as-is would create sharp steps and a spike of decisions in the late 2030s, so each year's capacity is spread over the surrounding 11 years with triangular weights (the year itself counts most, years 5 away count least). Any weight that would fall before 2026 or after 2050 is shifted onto the years that remain, so the total capacity is unchanged. Values are rounded to the nearest 1,000 metric tons, and the small rounding remainder is added to the peak year so the total stays exact. The unsmoothed schedule stays visible on the 'Derivation' tab.</t>
-  </si>
-  <si>
     <t>Limits and other regions</t>
   </si>
   <si>
@@ -273,6 +255,18 @@
   </si>
   <si>
     <t>Unit: metric tons clinker capacity/year</t>
+  </si>
+  <si>
+    <t>Annual rate (t/yr)</t>
+  </si>
+  <si>
+    <t>Remainder in 2040 (t/yr)</t>
+  </si>
+  <si>
+    <t>The older cohort (49.6 million metric tons) comes up for decision at 7% of its capacity per year starting in 2026, which is 3.472 million metric tons per year through 2039, with the remaining 0.992 million metric tons in 2040. The newer cohort (46.7 million metric tons) was installed over roughly 2000-2010 and reaches a 35-year campaign end across 2036-2045; we spread it evenly over those ten years at 4.67 million metric tons per year. The two cohorts overlap in 2036-2040. Turnover before 2025 is already reflected in the start-year capacity the model begins with, so nothing is scheduled before 2026.</t>
+  </si>
+  <si>
+    <t>Real kilns do not all reach a decision on the same date: campaign timing varies, and ECRA documents rolling 20-30 year component replacement cycles. Using the cohort schedule as-is would create sharp steps and a spike of decisions in the late 2030s, so each year's capacity is spread over the surrounding 11 years with triangular weights (the year itself counts most, years 5 away count least). Any weight that would fall before 2026 or after 2050 is shifted onto the years that remain, so the total capacity is unchanged. The unsmoothed schedule stays visible on the 'Derivation' tab.</t>
   </si>
 </sst>
 </file>
@@ -358,10 +352,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -668,122 +662,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="110.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.6328125" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B5" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="B8" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="7">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="B14" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="6">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="145" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="105" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{AFA434BE-8995-4B1F-BC02-12ECFA7989B5}"/>
-    <hyperlink ref="B14" r:id="rId2" xr:uid="{FFA3E5E4-20AA-438F-A1DE-78EE2F3821AC}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{F929486D-791A-4F3D-BF50-F24586553EDA}"/>
+    <hyperlink ref="B14" r:id="rId2" xr:uid="{0DF1D1FC-7969-4C3E-BAEE-5973FF6C9653}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -792,9 +787,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -808,7 +803,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -822,7 +817,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -844,14 +839,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -860,7 +855,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -869,107 +864,110 @@
         <v>3.4720000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5">
+        <f>B4*1000000</f>
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>15</v>
-      </c>
-      <c r="B5">
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
       </c>
       <c r="B6">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <f>B5*B6/1000000</f>
-        <v>48.58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48.608000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <f>B3-B7</f>
-        <v>1.0200000000000031</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.99199999999999733</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9">
+        <f>B8*1000000</f>
+        <v>991999.99999999732</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>19</v>
-      </c>
-      <c r="B9">
-        <v>1020000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>21</v>
       </c>
       <c r="B13">
         <f>'NZA Annex K Cohorts'!C3</f>
         <v>46.7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <f>B13/B14</f>
         <v>4.67</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16">
+        <f>B15*1000000</f>
+        <v>4670000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
-        <v>4700000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="C19" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2021</v>
       </c>
@@ -984,7 +982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2022</v>
       </c>
@@ -999,7 +997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -1014,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2024</v>
       </c>
@@ -1029,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2025</v>
       </c>
@@ -1044,252 +1042,252 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2026</v>
       </c>
       <c r="B25">
         <f t="shared" ref="B25:B38" si="1">$B$5</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2027</v>
       </c>
       <c r="B26">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2028</v>
       </c>
       <c r="B27">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2029</v>
       </c>
       <c r="B28">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2030</v>
       </c>
       <c r="B29">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2031</v>
       </c>
       <c r="B30">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2032</v>
       </c>
       <c r="B31">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2033</v>
       </c>
       <c r="B32">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2034</v>
       </c>
       <c r="B33">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2035</v>
       </c>
       <c r="B34">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
         <f t="shared" si="0"/>
-        <v>3470000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3472000.0000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2036</v>
       </c>
       <c r="B35">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C35">
         <f t="shared" ref="C35:C44" si="2">$B$16</f>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>8170000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8142000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2037</v>
       </c>
       <c r="B36">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C36">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>8170000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8142000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2038</v>
       </c>
       <c r="B37">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C37">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D37">
         <f t="shared" si="0"/>
-        <v>8170000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8142000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>2039</v>
       </c>
       <c r="B38">
         <f t="shared" si="1"/>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C38">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D38">
         <f t="shared" si="0"/>
-        <v>8170000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8142000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>2040</v>
       </c>
       <c r="B39">
         <f>$B$9</f>
-        <v>1020000</v>
+        <v>991999.99999999732</v>
       </c>
       <c r="C39">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>5720000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5661999.9999999972</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>2041</v>
       </c>
@@ -1298,14 +1296,14 @@
       </c>
       <c r="C40">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
-        <v>4700000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4670000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>2042</v>
       </c>
@@ -1314,14 +1312,14 @@
       </c>
       <c r="C41">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D41">
         <f t="shared" si="0"/>
-        <v>4700000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4670000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2043</v>
       </c>
@@ -1330,14 +1328,14 @@
       </c>
       <c r="C42">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
-        <v>4700000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4670000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2044</v>
       </c>
@@ -1346,14 +1344,14 @@
       </c>
       <c r="C43">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D43">
         <f t="shared" si="0"/>
-        <v>4700000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4670000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2045</v>
       </c>
@@ -1362,14 +1360,14 @@
       </c>
       <c r="C44">
         <f t="shared" si="2"/>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="D44">
         <f t="shared" si="0"/>
-        <v>4700000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4670000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2046</v>
       </c>
@@ -1384,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2047</v>
       </c>
@@ -1399,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2048</v>
       </c>
@@ -1414,7 +1412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2049</v>
       </c>
@@ -1429,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2050</v>
       </c>
@@ -1452,16 +1450,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>-5</v>
@@ -1497,9 +1495,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <f t="shared" ref="B4:L4" si="0">(6-ABS(B3))/36</f>
@@ -1546,23 +1544,23 @@
         <v>2.7777777777777776E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -1575,7 +1573,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -1588,7 +1586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -1601,7 +1599,7 @@
         <v>5.9999999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -1614,7 +1612,7 @@
         <v>3.6000000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2025</v>
       </c>
@@ -1627,267 +1625,267 @@
         <v>2.4000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2026</v>
       </c>
       <c r="B13">
         <f>Derivation!D25</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C13">
         <f t="shared" si="1"/>
         <v>1.7142857142857142</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2027</v>
       </c>
       <c r="B14">
         <f>Derivation!D26</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C14">
         <f t="shared" si="1"/>
         <v>1.3846153846153844</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2028</v>
       </c>
       <c r="B15">
         <f>Derivation!D27</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C15">
         <f t="shared" si="1"/>
         <v>1.1999999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2029</v>
       </c>
       <c r="B16">
         <f>Derivation!D28</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C16">
         <f t="shared" si="1"/>
         <v>1.0909090909090908</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2030</v>
       </c>
       <c r="B17">
         <f>Derivation!D29</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C17">
         <f t="shared" si="1"/>
         <v>1.0285714285714285</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2031</v>
       </c>
       <c r="B18">
         <f>Derivation!D30</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C18">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2032</v>
       </c>
       <c r="B19">
         <f>Derivation!D31</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C19">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2033</v>
       </c>
       <c r="B20">
         <f>Derivation!D32</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C20">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2034</v>
       </c>
       <c r="B21">
         <f>Derivation!D33</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C21">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2035</v>
       </c>
       <c r="B22">
         <f>Derivation!D34</f>
-        <v>3470000</v>
+        <v>3472000.0000000005</v>
       </c>
       <c r="C22">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>2036</v>
       </c>
       <c r="B23">
         <f>Derivation!D35</f>
-        <v>8170000</v>
+        <v>8142000</v>
       </c>
       <c r="C23">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>2037</v>
       </c>
       <c r="B24">
         <f>Derivation!D36</f>
-        <v>8170000</v>
+        <v>8142000</v>
       </c>
       <c r="C24">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>2038</v>
       </c>
       <c r="B25">
         <f>Derivation!D37</f>
-        <v>8170000</v>
+        <v>8142000</v>
       </c>
       <c r="C25">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>2039</v>
       </c>
       <c r="B26">
         <f>Derivation!D38</f>
-        <v>8170000</v>
+        <v>8142000</v>
       </c>
       <c r="C26">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>2040</v>
       </c>
       <c r="B27">
         <f>Derivation!D39</f>
-        <v>5720000</v>
+        <v>5661999.9999999972</v>
       </c>
       <c r="C27">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>2041</v>
       </c>
       <c r="B28">
         <f>Derivation!D40</f>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>2042</v>
       </c>
       <c r="B29">
         <f>Derivation!D41</f>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>2043</v>
       </c>
       <c r="B30">
         <f>Derivation!D42</f>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>2044</v>
       </c>
       <c r="B31">
         <f>Derivation!D43</f>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>2045</v>
       </c>
       <c r="B32">
         <f>Derivation!D44</f>
-        <v>4700000</v>
+        <v>4670000</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>2046</v>
       </c>
@@ -1900,7 +1898,7 @@
         <v>1.0285714285714282</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>2047</v>
       </c>
@@ -1913,7 +1911,7 @@
         <v>1.0909090909090906</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>2048</v>
       </c>
@@ -1926,7 +1924,7 @@
         <v>1.1999999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>2049</v>
       </c>
@@ -1939,7 +1937,7 @@
         <v>1.3846153846153844</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>2050</v>
       </c>
@@ -1952,59 +1950,59 @@
         <v>1.7142857142857142</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>36</v>
       </c>
-      <c r="C41" t="s">
+      <c r="G41" t="s">
         <v>37</v>
       </c>
-      <c r="D41" t="s">
+      <c r="H41" t="s">
         <v>38</v>
       </c>
-      <c r="E41" t="s">
+      <c r="I41" t="s">
         <v>39</v>
       </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>40</v>
       </c>
-      <c r="G41" t="s">
+      <c r="K41" t="s">
         <v>41</v>
       </c>
-      <c r="H41" t="s">
+      <c r="L41" t="s">
         <v>42</v>
       </c>
-      <c r="I41" t="s">
+      <c r="M41" t="s">
         <v>43</v>
       </c>
-      <c r="J41" t="s">
+      <c r="N41" t="s">
         <v>44</v>
       </c>
-      <c r="K41" t="s">
+      <c r="O41" t="s">
         <v>45</v>
       </c>
-      <c r="L41" t="s">
-        <v>46</v>
-      </c>
-      <c r="M41" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" t="s">
-        <v>48</v>
-      </c>
-      <c r="O41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>2021</v>
       </c>
@@ -2013,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <f t="shared" ref="C42:C71" si="3">ROUND(B42/1000,0)*1000</f>
+        <f t="shared" ref="C42:C71" si="3">(B42/1000)*1000</f>
         <v>0</v>
       </c>
       <c r="D42">
@@ -2022,7 +2020,7 @@
       </c>
       <c r="E42">
         <f t="shared" ref="E42:E71" si="5">IFERROR(INDEX($B$8:$B$37,MATCH(A42-B$3,$A$8:$A$37,0))*INDEX($C$8:$C$37,MATCH(A42-B$3,$A$8:$A$37,0))*B$4,0)</f>
-        <v>165238.09523809521</v>
+        <v>165333.33333333334</v>
       </c>
       <c r="F42">
         <f t="shared" ref="F42:F71" si="6">IFERROR(INDEX($B$8:$B$37,MATCH(A42-C$3,$A$8:$A$37,0))*INDEX($C$8:$C$37,MATCH(A42-C$3,$A$8:$A$37,0))*C$4,0)</f>
@@ -2065,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -2083,11 +2081,11 @@
       </c>
       <c r="E43">
         <f t="shared" si="5"/>
-        <v>133461.53846153844</v>
+        <v>133538.46153846153</v>
       </c>
       <c r="F43">
         <f t="shared" si="6"/>
-        <v>330476.19047619042</v>
+        <v>330666.66666666669</v>
       </c>
       <c r="G43">
         <f t="shared" si="7"/>
@@ -2126,7 +2124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>2023</v>
       </c>
@@ -2144,15 +2142,15 @@
       </c>
       <c r="E44">
         <f t="shared" si="5"/>
-        <v>115666.66666666663</v>
+        <v>115733.33333333331</v>
       </c>
       <c r="F44">
         <f t="shared" si="6"/>
-        <v>266923.07692307688</v>
+        <v>267076.92307692306</v>
       </c>
       <c r="G44">
         <f t="shared" si="7"/>
-        <v>495714.28571428568</v>
+        <v>496000.00000000006</v>
       </c>
       <c r="H44">
         <f t="shared" si="8"/>
@@ -2187,7 +2185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>2024</v>
       </c>
@@ -2205,19 +2203,19 @@
       </c>
       <c r="E45">
         <f t="shared" si="5"/>
-        <v>105151.51515151514</v>
+        <v>105212.12121212122</v>
       </c>
       <c r="F45">
         <f t="shared" si="6"/>
-        <v>231333.33333333326</v>
+        <v>231466.66666666663</v>
       </c>
       <c r="G45">
         <f t="shared" si="7"/>
-        <v>400384.61538461532</v>
+        <v>400615.38461538457</v>
       </c>
       <c r="H45">
         <f t="shared" si="8"/>
-        <v>660952.38095238083</v>
+        <v>661333.33333333337</v>
       </c>
       <c r="I45">
         <f t="shared" si="9"/>
@@ -2248,7 +2246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>2025</v>
       </c>
@@ -2266,23 +2264,23 @@
       </c>
       <c r="E46">
         <f t="shared" si="5"/>
-        <v>99142.85714285713</v>
+        <v>99200</v>
       </c>
       <c r="F46">
         <f t="shared" si="6"/>
-        <v>210303.03030303027</v>
+        <v>210424.24242424243</v>
       </c>
       <c r="G46">
         <f t="shared" si="7"/>
-        <v>346999.99999999988</v>
+        <v>347199.99999999994</v>
       </c>
       <c r="H46">
         <f t="shared" si="8"/>
-        <v>533846.15384615376</v>
+        <v>534153.84615384613</v>
       </c>
       <c r="I46">
         <f t="shared" si="9"/>
-        <v>826190.47619047621</v>
+        <v>826666.66666666686</v>
       </c>
       <c r="J46">
         <f t="shared" si="10"/>
@@ -2309,45 +2307,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>2026</v>
       </c>
       <c r="B47">
         <f t="shared" si="2"/>
-        <v>2731532.0790320784</v>
+        <v>2733106.4491064488</v>
       </c>
       <c r="C47">
         <f t="shared" si="3"/>
-        <v>2732000</v>
+        <v>2733106.4491064488</v>
       </c>
       <c r="D47">
         <f t="shared" si="4"/>
-        <v>2732000</v>
+        <v>2733106.4491064488</v>
       </c>
       <c r="E47">
         <f t="shared" si="5"/>
-        <v>96388.888888888861</v>
+        <v>96444.444444444423</v>
       </c>
       <c r="F47">
         <f t="shared" si="6"/>
-        <v>198285.71428571426</v>
+        <v>198400</v>
       </c>
       <c r="G47">
         <f t="shared" si="7"/>
-        <v>315454.54545454541</v>
+        <v>315636.36363636365</v>
       </c>
       <c r="H47">
         <f t="shared" si="8"/>
-        <v>462666.66666666651</v>
+        <v>462933.33333333326</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>667307.69230769225</v>
+        <v>667692.30769230763</v>
       </c>
       <c r="J47">
         <f t="shared" si="10"/>
-        <v>991428.57142857136</v>
+        <v>992000.00000000012</v>
       </c>
       <c r="K47">
         <f t="shared" si="11"/>
@@ -2370,49 +2368,49 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>2027</v>
       </c>
       <c r="B48">
         <f t="shared" si="2"/>
-        <v>3212494.3389943386</v>
+        <v>3214345.9207459209</v>
       </c>
       <c r="C48">
         <f t="shared" si="3"/>
-        <v>3212000</v>
+        <v>3214345.9207459209</v>
       </c>
       <c r="D48">
         <f t="shared" si="4"/>
-        <v>3212000</v>
+        <v>3214345.9207459209</v>
       </c>
       <c r="E48">
         <f t="shared" si="5"/>
-        <v>96388.888888888861</v>
+        <v>96444.444444444423</v>
       </c>
       <c r="F48">
         <f t="shared" si="6"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="G48">
         <f t="shared" si="7"/>
-        <v>297428.57142857136</v>
+        <v>297600</v>
       </c>
       <c r="H48">
         <f t="shared" si="8"/>
-        <v>420606.06060606055</v>
+        <v>420848.48484848486</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>578333.33333333326</v>
+        <v>578666.66666666663</v>
       </c>
       <c r="J48">
         <f t="shared" si="10"/>
-        <v>800769.23076923063</v>
+        <v>801230.76923076913</v>
       </c>
       <c r="K48">
         <f t="shared" si="11"/>
-        <v>826190.47619047621</v>
+        <v>826666.66666666686</v>
       </c>
       <c r="L48">
         <f t="shared" si="12"/>
@@ -2431,53 +2429,53 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>2028</v>
       </c>
       <c r="B49">
         <f t="shared" si="2"/>
-        <v>3522922.41092241</v>
+        <v>3524952.9137529135</v>
       </c>
       <c r="C49">
         <f t="shared" si="3"/>
-        <v>3523000</v>
+        <v>3524952.9137529135</v>
       </c>
       <c r="D49">
         <f t="shared" si="4"/>
-        <v>3523000</v>
+        <v>3524952.9137529135</v>
       </c>
       <c r="E49">
         <f t="shared" si="5"/>
-        <v>96388.888888888861</v>
+        <v>96444.444444444423</v>
       </c>
       <c r="F49">
         <f t="shared" si="6"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="G49">
         <f t="shared" si="7"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="H49">
         <f t="shared" si="8"/>
-        <v>396571.42857142852</v>
+        <v>396800</v>
       </c>
       <c r="I49">
         <f t="shared" si="9"/>
-        <v>525757.57575757569</v>
+        <v>526060.60606060608</v>
       </c>
       <c r="J49">
         <f t="shared" si="10"/>
-        <v>693999.99999999977</v>
+        <v>694399.99999999988</v>
       </c>
       <c r="K49">
         <f t="shared" si="11"/>
-        <v>667307.69230769225</v>
+        <v>667692.30769230763</v>
       </c>
       <c r="L49">
         <f t="shared" si="12"/>
-        <v>660952.38095238083</v>
+        <v>661333.33333333337</v>
       </c>
       <c r="M49">
         <f t="shared" si="13"/>
@@ -2492,57 +2490,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>2029</v>
       </c>
       <c r="B50">
         <f t="shared" si="2"/>
-        <v>3698406.0384060377</v>
+        <v>3700537.6845376841</v>
       </c>
       <c r="C50">
         <f t="shared" si="3"/>
-        <v>3698000</v>
+        <v>3700537.6845376841</v>
       </c>
       <c r="D50">
         <f t="shared" si="4"/>
-        <v>3698000</v>
+        <v>3700537.6845376841</v>
       </c>
       <c r="E50">
         <f t="shared" si="5"/>
-        <v>96388.888888888861</v>
+        <v>96444.444444444423</v>
       </c>
       <c r="F50">
         <f t="shared" si="6"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="G50">
         <f t="shared" si="7"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="H50">
         <f t="shared" si="8"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="I50">
         <f t="shared" si="9"/>
-        <v>495714.28571428568</v>
+        <v>496000</v>
       </c>
       <c r="J50">
         <f t="shared" si="10"/>
-        <v>630909.09090909082</v>
+        <v>631272.72727272729</v>
       </c>
       <c r="K50">
         <f t="shared" si="11"/>
-        <v>578333.33333333326</v>
+        <v>578666.66666666663</v>
       </c>
       <c r="L50">
         <f t="shared" si="12"/>
-        <v>533846.15384615376</v>
+        <v>534153.84615384613</v>
       </c>
       <c r="M50">
         <f t="shared" si="13"/>
-        <v>495714.28571428568</v>
+        <v>496000.00000000006</v>
       </c>
       <c r="N50">
         <f t="shared" si="14"/>
@@ -2553,692 +2551,692 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>2030</v>
       </c>
       <c r="B51">
         <f t="shared" si="2"/>
-        <v>3759975.5244755233</v>
+        <v>3762142.6573426565</v>
       </c>
       <c r="C51">
         <f t="shared" si="3"/>
-        <v>3760000</v>
+        <v>3762142.6573426565</v>
       </c>
       <c r="D51">
         <f t="shared" si="4"/>
-        <v>3760000</v>
+        <v>3762142.6573426565</v>
       </c>
       <c r="E51">
         <f t="shared" si="5"/>
-        <v>96388.888888888861</v>
+        <v>96444.444444444423</v>
       </c>
       <c r="F51">
         <f t="shared" si="6"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="G51">
         <f t="shared" si="7"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="H51">
         <f t="shared" si="8"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="I51">
         <f t="shared" si="9"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="J51">
         <f t="shared" si="10"/>
-        <v>594857.14285714272</v>
+        <v>595200</v>
       </c>
       <c r="K51">
         <f t="shared" si="11"/>
-        <v>525757.57575757569</v>
+        <v>526060.60606060608</v>
       </c>
       <c r="L51">
         <f t="shared" si="12"/>
-        <v>462666.66666666651</v>
+        <v>462933.33333333326</v>
       </c>
       <c r="M51">
         <f t="shared" si="13"/>
-        <v>400384.61538461532</v>
+        <v>400615.38461538457</v>
       </c>
       <c r="N51">
         <f t="shared" si="14"/>
-        <v>330476.19047619042</v>
+        <v>330666.66666666669</v>
       </c>
       <c r="O51">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>2031</v>
       </c>
       <c r="B52">
         <f t="shared" si="2"/>
-        <v>3850203.7407037402</v>
+        <v>3851514.2968142964</v>
       </c>
       <c r="C52">
         <f t="shared" si="3"/>
-        <v>3850000</v>
+        <v>3851514.2968142964</v>
       </c>
       <c r="D52">
         <f t="shared" si="4"/>
-        <v>3850000</v>
+        <v>3851514.2968142964</v>
       </c>
       <c r="E52">
         <f t="shared" si="5"/>
-        <v>226944.44444444438</v>
+        <v>226166.6666666666</v>
       </c>
       <c r="F52">
         <f t="shared" si="6"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="G52">
         <f t="shared" si="7"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="H52">
         <f t="shared" si="8"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="I52">
         <f t="shared" si="9"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="J52">
         <f t="shared" si="10"/>
-        <v>578333.33333333314</v>
+        <v>578666.66666666651</v>
       </c>
       <c r="K52">
         <f t="shared" si="11"/>
-        <v>495714.28571428568</v>
+        <v>496000</v>
       </c>
       <c r="L52">
         <f t="shared" si="12"/>
-        <v>420606.06060606055</v>
+        <v>420848.48484848486</v>
       </c>
       <c r="M52">
         <f t="shared" si="13"/>
-        <v>346999.99999999988</v>
+        <v>347199.99999999994</v>
       </c>
       <c r="N52">
         <f t="shared" si="14"/>
-        <v>266923.07692307688</v>
+        <v>267076.92307692306</v>
       </c>
       <c r="O52">
         <f t="shared" si="15"/>
-        <v>165238.09523809521</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+        <v>165333.33333333334</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>2032</v>
       </c>
       <c r="B53">
         <f t="shared" si="2"/>
-        <v>3974598.6235986226</v>
+        <v>3974163.7140637133</v>
       </c>
       <c r="C53">
         <f t="shared" si="3"/>
-        <v>3975000</v>
+        <v>3974163.7140637133</v>
       </c>
       <c r="D53">
         <f t="shared" si="4"/>
-        <v>3975000</v>
+        <v>3974163.7140637133</v>
       </c>
       <c r="E53">
         <f t="shared" si="5"/>
-        <v>226944.44444444438</v>
+        <v>226166.6666666666</v>
       </c>
       <c r="F53">
         <f t="shared" si="6"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="G53">
         <f t="shared" si="7"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="H53">
         <f t="shared" si="8"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="I53">
         <f t="shared" si="9"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="J53">
         <f t="shared" si="10"/>
-        <v>578333.33333333314</v>
+        <v>578666.66666666651</v>
       </c>
       <c r="K53">
         <f t="shared" si="11"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="L53">
         <f t="shared" si="12"/>
-        <v>396571.42857142852</v>
+        <v>396800</v>
       </c>
       <c r="M53">
         <f t="shared" si="13"/>
-        <v>315454.54545454541</v>
+        <v>315636.36363636365</v>
       </c>
       <c r="N53">
         <f t="shared" si="14"/>
-        <v>231333.33333333326</v>
+        <v>231466.66666666663</v>
       </c>
       <c r="O53">
         <f t="shared" si="15"/>
-        <v>133461.53846153844</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+        <v>133538.46153846153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>2033</v>
       </c>
       <c r="B54">
         <f t="shared" si="2"/>
-        <v>4298398.2683982672</v>
+        <v>4295424.2424242413</v>
       </c>
       <c r="C54">
         <f t="shared" si="3"/>
-        <v>4298000</v>
+        <v>4295424.2424242413</v>
       </c>
       <c r="D54">
         <f t="shared" si="4"/>
-        <v>4298000</v>
+        <v>4295424.2424242413</v>
       </c>
       <c r="E54">
         <f t="shared" si="5"/>
-        <v>226944.44444444438</v>
+        <v>226166.6666666666</v>
       </c>
       <c r="F54">
         <f t="shared" si="6"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="G54">
         <f t="shared" si="7"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="H54">
         <f t="shared" si="8"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="I54">
         <f t="shared" si="9"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="J54">
         <f t="shared" si="10"/>
-        <v>578333.33333333314</v>
+        <v>578666.66666666651</v>
       </c>
       <c r="K54">
         <f t="shared" si="11"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="L54">
         <f t="shared" si="12"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="M54">
         <f t="shared" si="13"/>
-        <v>297428.57142857136</v>
+        <v>297600</v>
       </c>
       <c r="N54">
         <f t="shared" si="14"/>
-        <v>210303.03030303027</v>
+        <v>210424.24242424243</v>
       </c>
       <c r="O54">
         <f t="shared" si="15"/>
-        <v>115666.66666666663</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+        <v>115733.33333333331</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>2034</v>
       </c>
       <c r="B55">
         <f t="shared" si="2"/>
-        <v>4789826.1183261182</v>
+        <v>4783501.0101010082</v>
       </c>
       <c r="C55">
         <f t="shared" si="3"/>
-        <v>4790000</v>
+        <v>4783501.0101010082</v>
       </c>
       <c r="D55">
         <f t="shared" si="4"/>
-        <v>4790000</v>
+        <v>4783501.0101010082</v>
       </c>
       <c r="E55">
         <f t="shared" si="5"/>
-        <v>226944.44444444438</v>
+        <v>226166.6666666666</v>
       </c>
       <c r="F55">
         <f t="shared" si="6"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="G55">
         <f t="shared" si="7"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="H55">
         <f t="shared" si="8"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="I55">
         <f t="shared" si="9"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="J55">
         <f t="shared" si="10"/>
-        <v>578333.33333333314</v>
+        <v>578666.66666666651</v>
       </c>
       <c r="K55">
         <f t="shared" si="11"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="L55">
         <f t="shared" si="12"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="M55">
         <f t="shared" si="13"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="N55">
         <f t="shared" si="14"/>
-        <v>198285.71428571426</v>
+        <v>198400</v>
       </c>
       <c r="O55">
         <f t="shared" si="15"/>
-        <v>105151.51515151514</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+        <v>105212.12121212122</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>2035</v>
       </c>
       <c r="B56">
         <f t="shared" si="2"/>
-        <v>5363031.7460317444</v>
+        <v>5351699.9999999991</v>
       </c>
       <c r="C56">
         <f t="shared" si="3"/>
-        <v>5363000</v>
+        <v>5351699.9999999991</v>
       </c>
       <c r="D56">
         <f t="shared" si="4"/>
-        <v>5363000</v>
+        <v>5351699.9999999991</v>
       </c>
       <c r="E56">
         <f t="shared" si="5"/>
-        <v>158888.88888888885</v>
+        <v>157277.77777777766</v>
       </c>
       <c r="F56">
         <f t="shared" si="6"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="G56">
         <f t="shared" si="7"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="H56">
         <f t="shared" si="8"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="I56">
         <f t="shared" si="9"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="J56">
         <f t="shared" si="10"/>
-        <v>578333.33333333314</v>
+        <v>578666.66666666651</v>
       </c>
       <c r="K56">
         <f t="shared" si="11"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="L56">
         <f t="shared" si="12"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="M56">
         <f t="shared" si="13"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="N56">
         <f t="shared" si="14"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="O56">
         <f t="shared" si="15"/>
-        <v>99142.85714285713</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+        <v>99200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>2036</v>
       </c>
       <c r="B57">
         <f t="shared" si="2"/>
-        <v>5979166.6666666651</v>
+        <v>5961944.4444444422</v>
       </c>
       <c r="C57">
         <f t="shared" si="3"/>
-        <v>5979000</v>
+        <v>5961944.4444444422</v>
       </c>
       <c r="D57">
         <f t="shared" si="4"/>
-        <v>5979000</v>
+        <v>5961944.4444444422</v>
       </c>
       <c r="E57">
         <f t="shared" si="5"/>
-        <v>130555.55555555552</v>
+        <v>129722.22222222219</v>
       </c>
       <c r="F57">
         <f t="shared" si="6"/>
-        <v>317777.77777777769</v>
+        <v>314555.55555555533</v>
       </c>
       <c r="G57">
         <f t="shared" si="7"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="H57">
         <f t="shared" si="8"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="I57">
         <f t="shared" si="9"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="J57">
         <f t="shared" si="10"/>
-        <v>1361666.6666666663</v>
+        <v>1356999.9999999995</v>
       </c>
       <c r="K57">
         <f t="shared" si="11"/>
-        <v>481944.44444444432</v>
+        <v>482222.22222222219</v>
       </c>
       <c r="L57">
         <f t="shared" si="12"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="M57">
         <f t="shared" si="13"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="N57">
         <f t="shared" si="14"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="O57">
         <f t="shared" si="15"/>
-        <v>96388.888888888861</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96444.444444444423</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>2037</v>
       </c>
       <c r="B58">
         <f t="shared" si="2"/>
-        <v>6371111.1111111101</v>
+        <v>6348777.7777777752</v>
       </c>
       <c r="C58">
         <f t="shared" si="3"/>
-        <v>6371000</v>
+        <v>6348777.7777777752</v>
       </c>
       <c r="D58">
         <f t="shared" si="4"/>
-        <v>6371000</v>
+        <v>6348777.7777777752</v>
       </c>
       <c r="E58">
         <f t="shared" si="5"/>
-        <v>130555.55555555552</v>
+        <v>129722.22222222219</v>
       </c>
       <c r="F58">
         <f t="shared" si="6"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="G58">
         <f t="shared" si="7"/>
-        <v>476666.66666666657</v>
+        <v>471833.33333333302</v>
       </c>
       <c r="H58">
         <f t="shared" si="8"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="I58">
         <f t="shared" si="9"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="J58">
         <f t="shared" si="10"/>
-        <v>1361666.6666666663</v>
+        <v>1356999.9999999995</v>
       </c>
       <c r="K58">
         <f t="shared" si="11"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="L58">
         <f t="shared" si="12"/>
-        <v>385555.55555555545</v>
+        <v>385777.77777777769</v>
       </c>
       <c r="M58">
         <f t="shared" si="13"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="N58">
         <f t="shared" si="14"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="O58">
         <f t="shared" si="15"/>
-        <v>96388.888888888861</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96444.444444444423</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>2038</v>
       </c>
       <c r="B59">
         <f t="shared" si="2"/>
-        <v>6536111.1111111101</v>
+        <v>6509444.4444444422</v>
       </c>
       <c r="C59">
         <f t="shared" si="3"/>
-        <v>6536000</v>
+        <v>6509444.4444444422</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>6536000</v>
+        <v>6509444.444444472</v>
       </c>
       <c r="E59">
         <f t="shared" si="5"/>
-        <v>130555.55555555552</v>
+        <v>129722.22222222219</v>
       </c>
       <c r="F59">
         <f t="shared" si="6"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="G59">
         <f t="shared" si="7"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="H59">
         <f t="shared" si="8"/>
-        <v>635555.55555555539</v>
+        <v>629111.11111111066</v>
       </c>
       <c r="I59">
         <f t="shared" si="9"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="J59">
         <f t="shared" si="10"/>
-        <v>1361666.6666666663</v>
+        <v>1356999.9999999995</v>
       </c>
       <c r="K59">
         <f t="shared" si="11"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="L59">
         <f t="shared" si="12"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="M59">
         <f t="shared" si="13"/>
-        <v>289166.66666666657</v>
+        <v>289333.33333333326</v>
       </c>
       <c r="N59">
         <f t="shared" si="14"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="O59">
         <f t="shared" si="15"/>
-        <v>96388.888888888861</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96444.444444444423</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>2039</v>
       </c>
       <c r="B60">
         <f t="shared" si="2"/>
-        <v>6474166.666666666</v>
+        <v>6443944.4444444422</v>
       </c>
       <c r="C60">
         <f t="shared" si="3"/>
-        <v>6474000</v>
+        <v>6443944.4444444422</v>
       </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>6474000</v>
+        <v>6443944.4444444422</v>
       </c>
       <c r="E60">
         <f t="shared" si="5"/>
-        <v>130555.55555555552</v>
+        <v>129722.22222222219</v>
       </c>
       <c r="F60">
         <f t="shared" si="6"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="G60">
         <f t="shared" si="7"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="H60">
         <f t="shared" si="8"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="I60">
         <f t="shared" si="9"/>
-        <v>794444.44444444438</v>
+        <v>786388.88888888841</v>
       </c>
       <c r="J60">
         <f t="shared" si="10"/>
-        <v>1361666.6666666663</v>
+        <v>1356999.9999999995</v>
       </c>
       <c r="K60">
         <f t="shared" si="11"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="L60">
         <f t="shared" si="12"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="M60">
         <f t="shared" si="13"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="N60">
         <f t="shared" si="14"/>
-        <v>192777.77777777772</v>
+        <v>192888.88888888885</v>
       </c>
       <c r="O60">
         <f t="shared" si="15"/>
-        <v>96388.888888888861</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96444.444444444423</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>2040</v>
       </c>
       <c r="B61">
         <f t="shared" si="2"/>
-        <v>6185277.7777777771</v>
+        <v>6152277.7777777752</v>
       </c>
       <c r="C61">
         <f t="shared" si="3"/>
-        <v>6185000</v>
+        <v>6152277.7777777752</v>
       </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>6185000</v>
+        <v>6152277.7777777752</v>
       </c>
       <c r="E61">
         <f t="shared" si="5"/>
-        <v>130555.55555555552</v>
+        <v>129722.22222222219</v>
       </c>
       <c r="F61">
         <f t="shared" si="6"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="G61">
         <f t="shared" si="7"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="H61">
         <f t="shared" si="8"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="I61">
         <f t="shared" si="9"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="J61">
         <f t="shared" si="10"/>
-        <v>953333.33333333314</v>
+        <v>943666.66666666605</v>
       </c>
       <c r="K61">
         <f t="shared" si="11"/>
-        <v>1134722.222222222</v>
+        <v>1130833.333333333</v>
       </c>
       <c r="L61">
         <f t="shared" si="12"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="M61">
         <f t="shared" si="13"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="N61">
         <f t="shared" si="14"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="O61">
         <f t="shared" si="15"/>
-        <v>96388.888888888861</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+        <v>96444.444444444423</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>2041</v>
       </c>
       <c r="B62">
         <f t="shared" si="2"/>
-        <v>5674999.9999999981</v>
+        <v>5642499.9999999991</v>
       </c>
       <c r="C62">
         <f t="shared" si="3"/>
-        <v>5675000</v>
+        <v>5642499.9999999991</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>5675000</v>
+        <v>5642499.9999999991</v>
       </c>
       <c r="E62">
         <f t="shared" si="5"/>
@@ -3246,60 +3244,60 @@
       </c>
       <c r="F62">
         <f t="shared" si="6"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="G62">
         <f t="shared" si="7"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="H62">
         <f t="shared" si="8"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="I62">
         <f t="shared" si="9"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="J62">
         <f t="shared" si="10"/>
-        <v>783333.33333333314</v>
+        <v>778333.33333333314</v>
       </c>
       <c r="K62">
         <f t="shared" si="11"/>
-        <v>794444.44444444438</v>
+        <v>786388.88888888841</v>
       </c>
       <c r="L62">
         <f t="shared" si="12"/>
-        <v>907777.77777777752</v>
+        <v>904666.6666666664</v>
       </c>
       <c r="M62">
         <f t="shared" si="13"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="N62">
         <f t="shared" si="14"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="O62">
         <f t="shared" si="15"/>
-        <v>226944.44444444438</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+        <v>226166.6666666666</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>2042</v>
       </c>
       <c r="B63">
         <f t="shared" si="2"/>
-        <v>4999999.9999999991</v>
+        <v>4969722.2222222211</v>
       </c>
       <c r="C63">
         <f t="shared" si="3"/>
-        <v>5000000</v>
+        <v>4969722.2222222211</v>
       </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>5000000</v>
+        <v>4969722.2222222211</v>
       </c>
       <c r="E63">
         <f t="shared" si="5"/>
@@ -3311,56 +3309,56 @@
       </c>
       <c r="G63">
         <f t="shared" si="7"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="H63">
         <f t="shared" si="8"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="I63">
         <f t="shared" si="9"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="J63">
         <f t="shared" si="10"/>
-        <v>783333.33333333314</v>
+        <v>778333.33333333314</v>
       </c>
       <c r="K63">
         <f t="shared" si="11"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="L63">
         <f t="shared" si="12"/>
-        <v>635555.55555555539</v>
+        <v>629111.11111111066</v>
       </c>
       <c r="M63">
         <f t="shared" si="13"/>
-        <v>680833.33333333314</v>
+        <v>678499.99999999977</v>
       </c>
       <c r="N63">
         <f t="shared" si="14"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="O63">
         <f t="shared" si="15"/>
-        <v>226944.44444444438</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+        <v>226166.6666666666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>2043</v>
       </c>
       <c r="B64">
         <f t="shared" si="2"/>
-        <v>4290833.3333333321</v>
+        <v>4263666.666666666</v>
       </c>
       <c r="C64">
         <f t="shared" si="3"/>
-        <v>4291000</v>
+        <v>4263666.666666666</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>4291000</v>
+        <v>4263666.666666666</v>
       </c>
       <c r="E64">
         <f t="shared" si="5"/>
@@ -3376,52 +3374,52 @@
       </c>
       <c r="H64">
         <f t="shared" si="8"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="I64">
         <f t="shared" si="9"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="J64">
         <f t="shared" si="10"/>
-        <v>783333.33333333314</v>
+        <v>778333.33333333314</v>
       </c>
       <c r="K64">
         <f t="shared" si="11"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="L64">
         <f t="shared" si="12"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="M64">
         <f t="shared" si="13"/>
-        <v>476666.66666666657</v>
+        <v>471833.33333333302</v>
       </c>
       <c r="N64">
         <f t="shared" si="14"/>
-        <v>453888.88888888876</v>
+        <v>452333.3333333332</v>
       </c>
       <c r="O64">
         <f t="shared" si="15"/>
-        <v>226944.44444444438</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+        <v>226166.6666666666</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>2044</v>
       </c>
       <c r="B65">
         <f t="shared" si="2"/>
-        <v>3547499.9999999991</v>
+        <v>3524333.3333333326</v>
       </c>
       <c r="C65">
         <f t="shared" si="3"/>
-        <v>3548000</v>
+        <v>3524333.3333333326</v>
       </c>
       <c r="D65">
         <f t="shared" si="4"/>
-        <v>3548000</v>
+        <v>3524333.3333333326</v>
       </c>
       <c r="E65">
         <f t="shared" si="5"/>
@@ -3441,48 +3439,48 @@
       </c>
       <c r="I65">
         <f t="shared" si="9"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="J65">
         <f t="shared" si="10"/>
-        <v>783333.33333333314</v>
+        <v>778333.33333333314</v>
       </c>
       <c r="K65">
         <f t="shared" si="11"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="L65">
         <f t="shared" si="12"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="M65">
         <f t="shared" si="13"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="N65">
         <f t="shared" si="14"/>
-        <v>317777.77777777769</v>
+        <v>314555.55555555533</v>
       </c>
       <c r="O65">
         <f t="shared" si="15"/>
-        <v>226944.44444444438</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+        <v>226166.6666666666</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>2045</v>
       </c>
       <c r="B66">
         <f t="shared" si="2"/>
-        <v>2769999.9999999995</v>
+        <v>2751722.2222222215</v>
       </c>
       <c r="C66">
         <f t="shared" si="3"/>
-        <v>2770000</v>
+        <v>2751722.2222222215</v>
       </c>
       <c r="D66">
         <f t="shared" si="4"/>
-        <v>2770000</v>
+        <v>2751722.2222222215</v>
       </c>
       <c r="E66">
         <f t="shared" si="5"/>
@@ -3506,44 +3504,44 @@
       </c>
       <c r="J66">
         <f t="shared" si="10"/>
-        <v>783333.33333333314</v>
+        <v>778333.33333333314</v>
       </c>
       <c r="K66">
         <f t="shared" si="11"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="L66">
         <f t="shared" si="12"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="M66">
         <f t="shared" si="13"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="N66">
         <f t="shared" si="14"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="O66">
         <f t="shared" si="15"/>
-        <v>158888.88888888885</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+        <v>157277.77777777766</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>2046</v>
       </c>
       <c r="B67">
         <f t="shared" si="2"/>
-        <v>1958333.3333333328</v>
+        <v>1945833.3333333328</v>
       </c>
       <c r="C67">
         <f t="shared" si="3"/>
-        <v>1958000</v>
+        <v>1945833.3333333328</v>
       </c>
       <c r="D67">
         <f t="shared" si="4"/>
-        <v>1958000</v>
+        <v>1945833.3333333328</v>
       </c>
       <c r="E67">
         <f t="shared" si="5"/>
@@ -3571,40 +3569,40 @@
       </c>
       <c r="K67">
         <f t="shared" si="11"/>
-        <v>652777.77777777764</v>
+        <v>648611.11111111101</v>
       </c>
       <c r="L67">
         <f t="shared" si="12"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="M67">
         <f t="shared" si="13"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="N67">
         <f t="shared" si="14"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="O67">
         <f t="shared" si="15"/>
-        <v>130555.55555555552</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129722.22222222219</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>2047</v>
       </c>
       <c r="B68">
         <f t="shared" si="2"/>
-        <v>1305555.5555555553</v>
+        <v>1297222.2222222218</v>
       </c>
       <c r="C68">
         <f t="shared" si="3"/>
-        <v>1306000</v>
+        <v>1297222.2222222218</v>
       </c>
       <c r="D68">
         <f t="shared" si="4"/>
-        <v>1306000</v>
+        <v>1297222.2222222218</v>
       </c>
       <c r="E68">
         <f t="shared" si="5"/>
@@ -3636,36 +3634,36 @@
       </c>
       <c r="L68">
         <f t="shared" si="12"/>
-        <v>522222.22222222207</v>
+        <v>518888.88888888876</v>
       </c>
       <c r="M68">
         <f t="shared" si="13"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="N68">
         <f t="shared" si="14"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="O68">
         <f t="shared" si="15"/>
-        <v>130555.55555555552</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129722.22222222219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>2048</v>
       </c>
       <c r="B69">
         <f t="shared" si="2"/>
-        <v>783333.33333333314</v>
+        <v>778333.33333333326</v>
       </c>
       <c r="C69">
         <f t="shared" si="3"/>
-        <v>783000</v>
+        <v>778333.33333333326</v>
       </c>
       <c r="D69">
         <f t="shared" si="4"/>
-        <v>783000</v>
+        <v>778333.33333333326</v>
       </c>
       <c r="E69">
         <f t="shared" si="5"/>
@@ -3701,32 +3699,32 @@
       </c>
       <c r="M69">
         <f t="shared" si="13"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="N69">
         <f t="shared" si="14"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="O69">
         <f t="shared" si="15"/>
-        <v>130555.55555555552</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129722.22222222219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>2049</v>
       </c>
       <c r="B70">
         <f t="shared" si="2"/>
-        <v>391666.66666666657</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="C70">
         <f t="shared" si="3"/>
-        <v>392000</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="D70">
         <f t="shared" si="4"/>
-        <v>392000</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="E70">
         <f t="shared" si="5"/>
@@ -3766,28 +3764,28 @@
       </c>
       <c r="N70">
         <f t="shared" si="14"/>
-        <v>261111.11111111104</v>
+        <v>259444.44444444438</v>
       </c>
       <c r="O70">
         <f t="shared" si="15"/>
-        <v>130555.55555555552</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129722.22222222219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>2050</v>
       </c>
       <c r="B71">
         <f t="shared" si="2"/>
-        <v>130555.55555555552</v>
+        <v>129722.22222222219</v>
       </c>
       <c r="C71">
         <f t="shared" si="3"/>
-        <v>131000</v>
+        <v>129722.2222222222</v>
       </c>
       <c r="D71">
         <f t="shared" si="4"/>
-        <v>131000</v>
+        <v>129722.2222222222</v>
       </c>
       <c r="E71">
         <f t="shared" si="5"/>
@@ -3831,21 +3829,21 @@
       </c>
       <c r="O71">
         <f t="shared" si="15"/>
-        <v>130555.55555555552</v>
-      </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+        <v>129722.22222222219</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B73">
         <f>SUM(B8:B37)-SUM(D42:D71)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B74" t="str">
         <f>IF(ABS(B73)&lt;0.5,"PASS","FAIL")</f>
@@ -3860,29 +3858,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="70.7265625" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B3" t="str">
         <f>IF(ABS(SUM(CPRS!B2:AE2)-SUM(Derivation!D20:D49))&lt;0.5,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B4" t="str">
         <f>IF(SUM(CPRS!B2:F5)=0,"PASS","FAIL")</f>
@@ -3900,11 +3898,11 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -3997,9 +3995,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <f>Smoothing!D42</f>
@@ -4023,108 +4021,108 @@
       </c>
       <c r="G2">
         <f>Smoothing!D47</f>
-        <v>2732000</v>
+        <v>2733106.4491064488</v>
       </c>
       <c r="H2">
         <f>Smoothing!D48</f>
-        <v>3212000</v>
+        <v>3214345.9207459209</v>
       </c>
       <c r="I2">
         <f>Smoothing!D49</f>
-        <v>3523000</v>
+        <v>3524952.9137529135</v>
       </c>
       <c r="J2">
         <f>Smoothing!D50</f>
-        <v>3698000</v>
+        <v>3700537.6845376841</v>
       </c>
       <c r="K2">
         <f>Smoothing!D51</f>
-        <v>3760000</v>
+        <v>3762142.6573426565</v>
       </c>
       <c r="L2">
         <f>Smoothing!D52</f>
-        <v>3850000</v>
+        <v>3851514.2968142964</v>
       </c>
       <c r="M2">
         <f>Smoothing!D53</f>
-        <v>3975000</v>
+        <v>3974163.7140637133</v>
       </c>
       <c r="N2">
         <f>Smoothing!D54</f>
-        <v>4298000</v>
+        <v>4295424.2424242413</v>
       </c>
       <c r="O2">
         <f>Smoothing!D55</f>
-        <v>4790000</v>
+        <v>4783501.0101010082</v>
       </c>
       <c r="P2">
         <f>Smoothing!D56</f>
-        <v>5363000</v>
+        <v>5351699.9999999991</v>
       </c>
       <c r="Q2">
         <f>Smoothing!D57</f>
-        <v>5979000</v>
+        <v>5961944.4444444422</v>
       </c>
       <c r="R2">
         <f>Smoothing!D58</f>
-        <v>6371000</v>
+        <v>6348777.7777777752</v>
       </c>
       <c r="S2">
         <f>Smoothing!D59</f>
-        <v>6536000</v>
+        <v>6509444.444444472</v>
       </c>
       <c r="T2">
         <f>Smoothing!D60</f>
-        <v>6474000</v>
+        <v>6443944.4444444422</v>
       </c>
       <c r="U2">
         <f>Smoothing!D61</f>
-        <v>6185000</v>
+        <v>6152277.7777777752</v>
       </c>
       <c r="V2">
         <f>Smoothing!D62</f>
-        <v>5675000</v>
+        <v>5642499.9999999991</v>
       </c>
       <c r="W2">
         <f>Smoothing!D63</f>
-        <v>5000000</v>
+        <v>4969722.2222222211</v>
       </c>
       <c r="X2">
         <f>Smoothing!D64</f>
-        <v>4291000</v>
+        <v>4263666.666666666</v>
       </c>
       <c r="Y2">
         <f>Smoothing!D65</f>
-        <v>3548000</v>
+        <v>3524333.3333333326</v>
       </c>
       <c r="Z2">
         <f>Smoothing!D66</f>
-        <v>2770000</v>
+        <v>2751722.2222222215</v>
       </c>
       <c r="AA2">
         <f>Smoothing!D67</f>
-        <v>1958000</v>
+        <v>1945833.3333333328</v>
       </c>
       <c r="AB2">
         <f>Smoothing!D68</f>
-        <v>1306000</v>
+        <v>1297222.2222222218</v>
       </c>
       <c r="AC2">
         <f>Smoothing!D69</f>
-        <v>783000</v>
+        <v>778333.33333333326</v>
       </c>
       <c r="AD2">
         <f>Smoothing!D70</f>
-        <v>392000</v>
+        <v>389166.66666666657</v>
       </c>
       <c r="AE2">
         <f>Smoothing!D71</f>
-        <v>131000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+        <v>129722.2222222222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -4217,9 +4215,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -4312,9 +4310,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>0</v>

--- a/InputData/indst/_cement/CPRS/Cement Preexisting Capacity Overhaul Decision Schedule.xlsx
+++ b/InputData/indst/_cement/CPRS/Cement Preexisting Capacity Overhaul Decision Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CPRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3994564B-B2A5-402E-8B06-62EC789A45BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFC1046-F0A7-476F-AFD1-F5B3A6E248A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="79">
   <si>
     <t>CPRS Cement Preexisting Capacity Overhaul Decision Schedule</t>
   </si>
@@ -267,6 +267,15 @@
   </si>
   <si>
     <t>Real kilns do not all reach a decision on the same date: campaign timing varies, and ECRA documents rolling 20-30 year component replacement cycles. Using the cohort schedule as-is would create sharp steps and a spike of decisions in the late 2030s, so each year's capacity is spread over the surrounding 11 years with triangular weights (the year itself counts most, years 5 away count least). Any weight that would fall before 2026 or after 2050 is shifted onto the years that remain, so the total capacity is unchanged. The unsmoothed schedule stays visible on the 'Derivation' tab.</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>The electric kiln with CCS is the electric kiln with a capture unit on its nearly pure CO2 stream, so it uses the electric kiln's value here (same kiln). Its capture is added through CCF (95 percent of calcination CO2 captured) and the CDSC capture inputs.</t>
   </si>
 </sst>
 </file>
@@ -339,7 +348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -355,8 +364,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -661,21 +676,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6328125" customWidth="1"/>
-    <col min="2" max="2" width="110.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.6328125" customWidth="1"/>
-    <col min="4" max="4" width="9.08984375" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="110.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -683,67 +698,67 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="7">
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="7">
         <v>2017</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
@@ -751,7 +766,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -759,7 +774,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -767,12 +782,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -787,9 +810,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,7 +826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -817,7 +840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -839,14 +862,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D49"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -855,7 +878,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -864,7 +887,7 @@
         <v>3.4720000000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
@@ -873,7 +896,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -881,7 +904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -890,7 +913,7 @@
         <v>48.608000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -899,7 +922,7 @@
         <v>0.99199999999999733</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -908,12 +931,12 @@
         <v>991999.99999999732</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -922,7 +945,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -930,7 +953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -939,7 +962,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -948,12 +971,12 @@
         <v>4670000</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -967,7 +990,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2021</v>
       </c>
@@ -982,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2022</v>
       </c>
@@ -997,7 +1020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2023</v>
       </c>
@@ -1012,7 +1035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2024</v>
       </c>
@@ -1027,7 +1050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2025</v>
       </c>
@@ -1042,7 +1065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2026</v>
       </c>
@@ -1058,7 +1081,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2027</v>
       </c>
@@ -1074,7 +1097,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2028</v>
       </c>
@@ -1090,7 +1113,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2029</v>
       </c>
@@ -1106,7 +1129,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2030</v>
       </c>
@@ -1122,7 +1145,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2031</v>
       </c>
@@ -1138,7 +1161,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2032</v>
       </c>
@@ -1154,7 +1177,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2033</v>
       </c>
@@ -1170,7 +1193,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2034</v>
       </c>
@@ -1186,7 +1209,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2035</v>
       </c>
@@ -1202,7 +1225,7 @@
         <v>3472000.0000000005</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2036</v>
       </c>
@@ -1219,7 +1242,7 @@
         <v>8142000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2037</v>
       </c>
@@ -1236,7 +1259,7 @@
         <v>8142000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2038</v>
       </c>
@@ -1253,7 +1276,7 @@
         <v>8142000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2039</v>
       </c>
@@ -1270,7 +1293,7 @@
         <v>8142000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2040</v>
       </c>
@@ -1287,7 +1310,7 @@
         <v>5661999.9999999972</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2041</v>
       </c>
@@ -1303,7 +1326,7 @@
         <v>4670000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2042</v>
       </c>
@@ -1319,7 +1342,7 @@
         <v>4670000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2043</v>
       </c>
@@ -1335,7 +1358,7 @@
         <v>4670000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2044</v>
       </c>
@@ -1351,7 +1374,7 @@
         <v>4670000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2045</v>
       </c>
@@ -1367,7 +1390,7 @@
         <v>4670000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2046</v>
       </c>
@@ -1382,7 +1405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2047</v>
       </c>
@@ -1397,7 +1420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2048</v>
       </c>
@@ -1412,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2049</v>
       </c>
@@ -1427,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2050</v>
       </c>
@@ -1450,14 +1473,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O74"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1495,7 +1518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -1544,12 +1567,12 @@
         <v>2.7777777777777776E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1560,7 +1583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2021</v>
       </c>
@@ -1573,7 +1596,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2022</v>
       </c>
@@ -1586,7 +1609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -1599,7 +1622,7 @@
         <v>5.9999999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2024</v>
       </c>
@@ -1612,7 +1635,7 @@
         <v>3.6000000000000005</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2025</v>
       </c>
@@ -1625,7 +1648,7 @@
         <v>2.4000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2026</v>
       </c>
@@ -1638,7 +1661,7 @@
         <v>1.7142857142857142</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2027</v>
       </c>
@@ -1651,7 +1674,7 @@
         <v>1.3846153846153844</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2028</v>
       </c>
@@ -1664,7 +1687,7 @@
         <v>1.1999999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2029</v>
       </c>
@@ -1677,7 +1700,7 @@
         <v>1.0909090909090908</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2030</v>
       </c>
@@ -1690,7 +1713,7 @@
         <v>1.0285714285714285</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2031</v>
       </c>
@@ -1703,7 +1726,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2032</v>
       </c>
@@ -1716,7 +1739,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2033</v>
       </c>
@@ -1729,7 +1752,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2034</v>
       </c>
@@ -1742,7 +1765,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2035</v>
       </c>
@@ -1755,7 +1778,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2036</v>
       </c>
@@ -1768,7 +1791,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2037</v>
       </c>
@@ -1781,7 +1804,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2038</v>
       </c>
@@ -1794,7 +1817,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2039</v>
       </c>
@@ -1807,7 +1830,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2040</v>
       </c>
@@ -1820,7 +1843,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2041</v>
       </c>
@@ -1833,7 +1856,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2042</v>
       </c>
@@ -1846,7 +1869,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2043</v>
       </c>
@@ -1859,7 +1882,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2044</v>
       </c>
@@ -1872,7 +1895,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2045</v>
       </c>
@@ -1885,7 +1908,7 @@
         <v>0.99999999999999978</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2046</v>
       </c>
@@ -1898,7 +1921,7 @@
         <v>1.0285714285714282</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2047</v>
       </c>
@@ -1911,7 +1934,7 @@
         <v>1.0909090909090906</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2048</v>
       </c>
@@ -1924,7 +1947,7 @@
         <v>1.1999999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2049</v>
       </c>
@@ -1937,7 +1960,7 @@
         <v>1.3846153846153844</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2050</v>
       </c>
@@ -1950,12 +1973,12 @@
         <v>1.7142857142857142</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -2002,7 +2025,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2021</v>
       </c>
@@ -2063,7 +2086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -2124,7 +2147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2023</v>
       </c>
@@ -2185,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2024</v>
       </c>
@@ -2246,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2025</v>
       </c>
@@ -2307,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2026</v>
       </c>
@@ -2368,7 +2391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2027</v>
       </c>
@@ -2429,7 +2452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2028</v>
       </c>
@@ -2490,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2029</v>
       </c>
@@ -2551,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2030</v>
       </c>
@@ -2612,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2031</v>
       </c>
@@ -2673,7 +2696,7 @@
         <v>165333.33333333334</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2032</v>
       </c>
@@ -2734,7 +2757,7 @@
         <v>133538.46153846153</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2033</v>
       </c>
@@ -2795,7 +2818,7 @@
         <v>115733.33333333331</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2034</v>
       </c>
@@ -2856,7 +2879,7 @@
         <v>105212.12121212122</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2035</v>
       </c>
@@ -2917,7 +2940,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2036</v>
       </c>
@@ -2978,7 +3001,7 @@
         <v>96444.444444444423</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2037</v>
       </c>
@@ -3039,7 +3062,7 @@
         <v>96444.444444444423</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2038</v>
       </c>
@@ -3100,7 +3123,7 @@
         <v>96444.444444444423</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2039</v>
       </c>
@@ -3161,7 +3184,7 @@
         <v>96444.444444444423</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2040</v>
       </c>
@@ -3222,7 +3245,7 @@
         <v>96444.444444444423</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2041</v>
       </c>
@@ -3283,7 +3306,7 @@
         <v>226166.6666666666</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2042</v>
       </c>
@@ -3344,7 +3367,7 @@
         <v>226166.6666666666</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2043</v>
       </c>
@@ -3405,7 +3428,7 @@
         <v>226166.6666666666</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2044</v>
       </c>
@@ -3466,7 +3489,7 @@
         <v>226166.6666666666</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2045</v>
       </c>
@@ -3527,7 +3550,7 @@
         <v>157277.77777777766</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2046</v>
       </c>
@@ -3588,7 +3611,7 @@
         <v>129722.22222222219</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2047</v>
       </c>
@@ -3649,7 +3672,7 @@
         <v>129722.22222222219</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2048</v>
       </c>
@@ -3710,7 +3733,7 @@
         <v>129722.22222222219</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2049</v>
       </c>
@@ -3771,7 +3794,7 @@
         <v>129722.22222222219</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2050</v>
       </c>
@@ -3832,7 +3855,7 @@
         <v>129722.22222222219</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>46</v>
       </c>
@@ -3841,7 +3864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>47</v>
       </c>
@@ -3858,18 +3881,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.7265625" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
+    <col min="1" max="1" width="70.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -3878,12 +3901,12 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
       <c r="B4" t="str">
-        <f>IF(SUM(CPRS!B2:F5)=0,"PASS","FAIL")</f>
+        <f>IF(SUM(CPRS!B2:F6)=0,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -3897,10 +3920,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>71</v>
       </c>
@@ -3995,7 +4018,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -4120,7 +4143,7 @@
         <v>129722.2222222222</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -4215,7 +4238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -4310,98 +4333,223 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>D4</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>G4</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>H4</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>I4</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>J4</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>K4</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>L4</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>M4</f>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f>N4</f>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <f>O4</f>
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <f>P4</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>Q4</f>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <f>R4</f>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <f>S4</f>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f>T4</f>
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f>U4</f>
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <f>V4</f>
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <f>W4</f>
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <f>X4</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <f>Y4</f>
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <f>Z4</f>
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <f>AA4</f>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f>AB4</f>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f>AC4</f>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f>AD4</f>
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <f>AE4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>51</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
         <v>0</v>
       </c>
     </row>
